--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N79_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N79_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>65.71793665306325</v>
+        <v>10.67916470612278</v>
       </c>
       <c r="D2" t="n">
-        <v>65.83793950004738</v>
+        <v>10.6986651687577</v>
       </c>
       <c r="E2" t="n">
-        <v>15.97112373814036</v>
+        <v>2.595307607447809</v>
       </c>
       <c r="F2" t="n">
-        <v>14.78293010814498</v>
+        <v>2.40222614257356</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>52.27423074740125</v>
+        <v>8.494562496452703</v>
       </c>
       <c r="D3" t="n">
-        <v>35.38551178723355</v>
+        <v>5.750145665425451</v>
       </c>
       <c r="E3" t="n">
-        <v>15.97112373814036</v>
+        <v>2.595307607447809</v>
       </c>
       <c r="F3" t="n">
-        <v>14.78293010814498</v>
+        <v>2.40222614257356</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>59.94086726556257</v>
+        <v>9.740390930653918</v>
       </c>
       <c r="D4" t="n">
-        <v>28.81221854592389</v>
+        <v>4.681985513712632</v>
       </c>
       <c r="E4" t="n">
-        <v>15.97112373814036</v>
+        <v>2.595307607447809</v>
       </c>
       <c r="F4" t="n">
-        <v>14.78293010814498</v>
+        <v>2.40222614257356</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>61.22633794295075</v>
+        <v>9.949279915729496</v>
       </c>
       <c r="D5" t="n">
-        <v>15.83745664220791</v>
+        <v>2.573586704358786</v>
       </c>
       <c r="E5" t="n">
-        <v>15.97112373814036</v>
+        <v>2.595307607447809</v>
       </c>
       <c r="F5" t="n">
-        <v>14.78293010814498</v>
+        <v>2.40222614257356</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>48.46025932350228</v>
+        <v>7.87479214006912</v>
       </c>
       <c r="D6" t="n">
-        <v>15.75247996348511</v>
+        <v>2.559777994066331</v>
       </c>
       <c r="E6" t="n">
-        <v>15.97112373814036</v>
+        <v>2.595307607447809</v>
       </c>
       <c r="F6" t="n">
-        <v>14.78293010814498</v>
+        <v>2.40222614257356</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>37.70718393127098</v>
+        <v>6.127417388831535</v>
       </c>
       <c r="D7" t="n">
-        <v>11.29650880188703</v>
+        <v>1.835682680306642</v>
       </c>
       <c r="E7" t="n">
-        <v>15.97112373814036</v>
+        <v>2.595307607447809</v>
       </c>
       <c r="F7" t="n">
-        <v>14.78293010814498</v>
+        <v>2.40222614257356</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>26.53063210703112</v>
+        <v>4.311227717392557</v>
       </c>
       <c r="D8" t="n">
-        <v>26.32486121791264</v>
+        <v>4.277789947910804</v>
       </c>
       <c r="E8" t="n">
-        <v>15.97112373814036</v>
+        <v>2.595307607447809</v>
       </c>
       <c r="F8" t="n">
-        <v>14.78293010814498</v>
+        <v>2.40222614257356</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>27.41601769646728</v>
+        <v>4.455102875675933</v>
       </c>
       <c r="D9" t="n">
-        <v>22.48950372457733</v>
+        <v>3.654544355243817</v>
       </c>
       <c r="E9" t="n">
-        <v>15.97112373814036</v>
+        <v>2.595307607447809</v>
       </c>
       <c r="F9" t="n">
-        <v>14.78293010814498</v>
+        <v>2.40222614257356</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>40.87654564488393</v>
+        <v>6.642438667293638</v>
       </c>
       <c r="D10" t="n">
-        <v>41.02639375827502</v>
+        <v>6.666788985719691</v>
       </c>
       <c r="E10" t="n">
-        <v>15.97112373814036</v>
+        <v>2.595307607447809</v>
       </c>
       <c r="F10" t="n">
-        <v>14.78293010814498</v>
+        <v>2.40222614257356</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>32.43520810299385</v>
+        <v>5.270721316736502</v>
       </c>
       <c r="D11" t="n">
-        <v>35.23274201343079</v>
+        <v>5.725320577182504</v>
       </c>
       <c r="E11" t="n">
-        <v>15.97112373814036</v>
+        <v>2.595307607447809</v>
       </c>
       <c r="F11" t="n">
-        <v>14.78293010814498</v>
+        <v>2.40222614257356</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>11.77531618003179</v>
+        <v>1.913488879255166</v>
       </c>
       <c r="D12" t="n">
-        <v>13.32302728471293</v>
+        <v>2.164991933765852</v>
       </c>
       <c r="E12" t="n">
-        <v>15.97112373814036</v>
+        <v>2.595307607447809</v>
       </c>
       <c r="F12" t="n">
-        <v>14.78293010814498</v>
+        <v>2.40222614257356</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>28.07123935757884</v>
+        <v>4.561576395606561</v>
       </c>
       <c r="D13" t="n">
-        <v>38.15438260296998</v>
+        <v>6.200087172982622</v>
       </c>
       <c r="E13" t="n">
-        <v>15.97112373814036</v>
+        <v>2.595307607447809</v>
       </c>
       <c r="F13" t="n">
-        <v>14.78293010814498</v>
+        <v>2.40222614257356</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
